--- a/docs/ReFood_ProductBacklog.xlsx
+++ b/docs/ReFood_ProductBacklog.xlsx
@@ -22,27 +22,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="163">
   <si>
     <t xml:space="preserve">🌿  ReFood  —  Product Backlog</t>
   </si>
   <si>
-    <t xml:space="preserve">Redução do Desperdício de Alimentos  |  Engenharia de Software 2026  |  Arthur Brasil · Guilherme Luiz · Henrique Borges · Lucas Lonardi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
+    <t xml:space="preserve">Redução do Desperdício de Alimentos  |  Engenharia de Software 2026  |  Arthur Brasil · Lucas Lonardi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
   </si>
   <si>
     <t xml:space="preserve">6</t>
   </si>
   <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58 SP</t>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65 SP</t>
   </si>
   <si>
     <t xml:space="preserve">4</t>
@@ -120,127 +120,157 @@
     <t xml:space="preserve">Entrevista</t>
   </si>
   <si>
+    <t xml:space="preserve">Fora de escopo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descontinuado — redução de escopo após saída de Guilherme e Henrique (equipe passou a ser 2 pessoas); ReFood tornou-se despensa única sem contas de usuário.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como usuário cadastrado, quero fazer login com e-mail e senha para acessar meus dados com segurança.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login funcional, sessão mantida, mensagem de erro em dados inválidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RF02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ver observação em US-01.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como usuário, quero recuperar minha senha por e-mail para não perder acesso à minha conta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-mail enviado em até 1 min, link de redefinição funcional por 24h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Media</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Questionário</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como usuário, quero cadastrar um alimento informando nome, categoria, quantidade, unidade e data de validade para controlar meu estoque.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todos os campos obrigatórios validados, item aparece na listagem imediatamente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RF03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 1 (executado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concluído</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equivale a US-01 no Sprint Backlog executado (2 pessoas).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como usuário, quero visualizar a lista completa dos meus alimentos, podendo filtrar por categoria e ordenar por validade, para encontrar itens rapidamente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filtros funcionais, badges de status por cor, ordenação correta por data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RF06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equivale a US-02 no Sprint Backlog executado (2 pessoas).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como usuário, quero atualizar a data de validade de um alimento para corrigir informações incorretas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edição salva corretamente, data refletida nos alertas em tempo real</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RF04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equivale a US-05 no Sprint Backlog executado (reestimado de 3 para 2 SP).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como usuário, quero editar os dados de um alimento cadastrado para manter as informações sempre corretas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todos os campos editáveis, alterações persistem após fechar o app</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RF05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Análise Similares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equivale a US-03 no Sprint Backlog executado (2 pessoas).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como usuário, quero excluir um alimento do estoque para remover itens consumidos ou descartados.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmação antes de deletar, item removido da lista imediatamente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equivale a US-04 no Sprint Backlog executado (2 pessoas).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como usuário, quero receber notificações automáticas quando um alimento estiver próximo ao vencimento para não perder prazos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notificação disparada conforme antecedência configurada, push notification funcionando em Android e iOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RF07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">A Fazer</t>
   </si>
   <si>
-    <t xml:space="preserve">US-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como usuário cadastrado, quero fazer login com e-mail e senha para acessar meus dados com segurança.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Login funcional, sessão mantida, mensagem de erro em dados inválidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como usuário, quero recuperar minha senha por e-mail para não perder acesso à minha conta.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-mail enviado em até 1 min, link de redefinição funcional por 24h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Media</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Questionário</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como usuário, quero cadastrar um alimento informando nome, categoria, quantidade, unidade e data de validade para controlar meu estoque.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Todos os campos obrigatórios validados, item aparece na listagem imediatamente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como usuário, quero visualizar a lista completa dos meus alimentos, podendo filtrar por categoria e ordenar por validade, para encontrar itens rapidamente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filtros funcionais, badges de status por cor, ordenação correta por data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como usuário, quero atualizar a data de validade de um alimento para corrigir informações incorretas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edição salva corretamente, data refletida nos alertas em tempo real</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como usuário, quero editar os dados de um alimento cadastrado para manter as informações sempre corretas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Todos os campos editáveis, alterações persistem após fechar o app</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Análise Similares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como usuário, quero excluir um alimento do estoque para remover itens consumidos ou descartados.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirmação antes de deletar, item removido da lista imediatamente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como usuário, quero receber notificações automáticas quando um alimento estiver próximo ao vencimento para não perder prazos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notificação disparada conforme antecedência configurada, push notification funcionando em Android e iOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF07</t>
+    <t xml:space="preserve">Versão visual (badges) já entregue antecipadamente como US-06 no Sprint 1. Reestimado pra 5 SP: MVP com expo-notifications local, sem configuração de antecedência (isso fica na US-10, adiada).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como usuário, quero configurar com quantos dias de antecedência quero ser alertado (1 a 7 dias) para personalizar minha experiência.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slider/seletor de 1 a 7 dias, configuração salva por alimento, padrão 3 dias</t>
   </si>
   <si>
     <t xml:space="preserve">Sprint 3</t>
   </si>
   <si>
-    <t xml:space="preserve">US-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como usuário, quero configurar com quantos dias de antecedência quero ser alertado (1 a 7 dias) para personalizar minha experiência.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slider/seletor de 1 a 7 dias, configuração salva por alimento, padrão 3 dias</t>
+    <t xml:space="preserve">Adiada: entra depois da notificação básica (US-09) estar funcionando.</t>
   </si>
   <si>
     <t xml:space="preserve">US-11</t>
@@ -255,6 +285,9 @@
     <t xml:space="preserve">RF08</t>
   </si>
   <si>
+    <t xml:space="preserve">Sugestão automática depende do histórico de consumo (US-12/US-13).</t>
+  </si>
+  <si>
     <t xml:space="preserve">US-12</t>
   </si>
   <si>
@@ -267,28 +300,58 @@
     <t xml:space="preserve">RF09</t>
   </si>
   <si>
+    <t xml:space="preserve">Em andamento (backend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend implementado nesta sessão (GET /relatorios/desperdicio + vw_desperdicio_por_categoria); falta a tela mobile.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como usuário, quero registrar um alimento como "consumido" ou "descartado" para que o sistema contabilize no relatório.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ação registrada com data e tipo, impacto visível no relatório do período</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elevada de Baixa pra Alta: é o dado bruto de que o relatório (US-12) depende. Backend implementado (historico_alimentos gravado em DELETE /alimentos/:id); falta o modal de confirmação no mobile.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como usuário, quero compartilhar minha lista de compras com outros membros da casa para facilitar as compras em família.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lista compartilhável via link ou contato, atualizações em tempo real para todos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baixa</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sprint 4</t>
   </si>
   <si>
-    <t xml:space="preserve">US-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como usuário, quero registrar um alimento como "consumido" ou "descartado" para que o sistema contabilize no relatório.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ação registrada com data e tipo, impacto visível no relatório do período</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baixa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como usuário, quero compartilhar minha lista de compras com outros membros da casa para facilitar as compras em família.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lista compartilhável via link ou contato, atualizações em tempo real para todos</t>
+    <t xml:space="preserve">Depende de autenticação (US-01/02/03), que foi cortada na redução de escopo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como equipe, queremos testes automatizados no backend para garantir que mudanças futuras não quebrem funcionalidades existentes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suíte Jest + Supertest cobrindo os endpoints de alimentos e categorias; script npm test funcional; roda contra uma branch de banco isolada no Neon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RNF-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova story — não existia no backlog original (equipe de 4 pessoas não tinha essa frente listada).</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL DE STORY POINTS</t>
@@ -384,9 +447,6 @@
     <t xml:space="preserve">Compatibilidade</t>
   </si>
   <si>
-    <t xml:space="preserve">RNF-06</t>
-  </si>
-  <si>
     <t xml:space="preserve">Manutenibilidade</t>
   </si>
   <si>
@@ -448,6 +508,9 @@
   </si>
   <si>
     <t xml:space="preserve">TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nota: este era o plano original com 4 pessoas (58 SP). Após a redução da equipe para 2 (Arthur e Lucas), a execução real seguiu outro sequenciamento — ver aba 'Product Backlog' (coluna Status/Observações) e docs/ReFood_SprintBacklog.xlsx para o que foi de fato entregue (Sprint 1, 23 SP) e o que está em andamento (Sprint 2).</t>
   </si>
 </sst>
 </file>
@@ -459,7 +522,7 @@
     <numFmt numFmtId="165" formatCode="General"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -638,7 +701,7 @@
     <font>
       <b val="true"/>
       <sz val="9"/>
-      <color rgb="FF3B6D11"/>
+      <color rgb="FF6B7280"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -660,8 +723,24 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF2D6A4F"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF5B21B6"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF3B6D11"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -676,6 +755,14 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF854F0B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF92400E"/>
       <name val="Arial"/>
@@ -706,8 +793,16 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF6B7280"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -735,7 +830,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEAF3DE"/>
-        <bgColor rgb="FFFAEEDA"/>
+        <bgColor rgb="FFF3F4F6"/>
       </patternFill>
     </fill>
     <fill>
@@ -776,6 +871,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF3F4F6"/>
+        <bgColor rgb="FFF4FAF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0FBF3"/>
         <bgColor rgb="FFF4FAF6"/>
       </patternFill>
@@ -783,7 +884,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEDE9FE"/>
-        <bgColor rgb="FFDBEAFE"/>
+        <bgColor rgb="FFF3F4F6"/>
       </patternFill>
     </fill>
     <fill>
@@ -891,11 +992,15 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="58">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -904,11 +1009,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -996,7 +1101,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1004,27 +1109,27 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1032,19 +1137,31 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1060,35 +1177,35 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="15" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="16" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="35" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="35" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1102,6 +1219,10 @@
     </xf>
     <xf numFmtId="166" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1120,7 +1241,7 @@
       <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFF4FAF6"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
@@ -1130,7 +1251,7 @@
       <rgbColor rgb="FF5B21B6"/>
       <rgbColor rgb="FF2D6A4F"/>
       <rgbColor rgb="FFB7E4C7"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF4A6358"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FFA32D2D"/>
       <rgbColor rgb="FFFEF3C7"/>
@@ -1153,7 +1274,7 @@
       <rgbColor rgb="FFFAEEDA"/>
       <rgbColor rgb="FFEDE9FE"/>
       <rgbColor rgb="FFEAF3DE"/>
-      <rgbColor rgb="FFF4FAF6"/>
+      <rgbColor rgb="FFF3F4F6"/>
       <rgbColor rgb="FFFCEBEB"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
@@ -1161,7 +1282,7 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF4A6358"/>
+      <rgbColor rgb="FF6B7280"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
@@ -1357,627 +1478,687 @@
     <tabColor rgb="FF2D6A4F"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="6" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="7" t="s">
+      <c r="D5" s="7"/>
+      <c r="E5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="8" t="s">
+      <c r="F5" s="8"/>
+      <c r="G5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="8"/>
-      <c r="I5" s="9" t="s">
+      <c r="H5" s="9"/>
+      <c r="I5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="12" t="s">
+      <c r="B6" s="12"/>
+      <c r="C6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="13" t="s">
+      <c r="D6" s="13"/>
+      <c r="E6" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="14" t="s">
+      <c r="F6" s="14"/>
+      <c r="G6" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="14"/>
-      <c r="I6" s="15" t="s">
+      <c r="H6" s="15"/>
+      <c r="I6" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="J6" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="18" t="s">
+      <c r="H10" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="18" t="s">
+      <c r="I10" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="18" t="s">
+      <c r="J10" s="19" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G11" s="24" t="s">
+      <c r="F11" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="25" t="s">
+      <c r="H11" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="I11" s="26" t="s">
+      <c r="I11" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="27"/>
+      <c r="J11" s="28" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="29" t="s">
+      <c r="A12" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="B12" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="C12" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="D12" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="31" t="s">
+      <c r="F12" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" s="34" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" s="28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="J14" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="G12" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" s="32" t="s">
+      <c r="G15" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="I12" s="26" t="s">
+      <c r="I15" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="J15" s="28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="I16" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="J16" s="34" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="J17" s="28" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="I18" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="J18" s="34" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="J19" s="28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" s="39" t="s">
+        <v>81</v>
+      </c>
+      <c r="H20" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="I20" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="J20" s="34" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="I21" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="J21" s="28" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="H22" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="40" t="s">
+        <v>92</v>
+      </c>
+      <c r="J22" s="34" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="H23" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="40" t="s">
+        <v>92</v>
+      </c>
+      <c r="J23" s="28" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="F24" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="H24" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="I24" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="J12" s="33"/>
-    </row>
-    <row r="13" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="23" t="s">
+      <c r="J24" s="34" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E25" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="G13" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="I13" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="J13" s="27"/>
-    </row>
-    <row r="14" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="F14" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="J14" s="33"/>
-    </row>
-    <row r="15" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="H15" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="J15" s="27"/>
-    </row>
-    <row r="16" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="G16" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="H16" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="I16" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="J16" s="33"/>
-    </row>
-    <row r="17" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="F17" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="G17" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="H17" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I17" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="J17" s="27"/>
-    </row>
-    <row r="18" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D18" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="E18" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="G18" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="H18" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="I18" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="J18" s="33"/>
-    </row>
-    <row r="19" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
+      <c r="G25" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="H25" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="I25" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="J25" s="28" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="44" t="n">
+        <f aca="false">SUM(F11:F25)</f>
         <v>65</v>
       </c>
-      <c r="B19" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="G19" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="H19" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="J19" s="27"/>
-    </row>
-    <row r="20" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="D20" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="E20" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="F20" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="G20" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="H20" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="I20" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="J20" s="33"/>
-    </row>
-    <row r="21" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="H21" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I21" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="J21" s="27"/>
-    </row>
-    <row r="22" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="B22" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="F22" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="G22" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="H22" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="J22" s="33"/>
-    </row>
-    <row r="23" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="E23" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="F23" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="G23" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="H23" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="J23" s="27"/>
-    </row>
-    <row r="24" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="B24" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="D24" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E24" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="F24" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="H24" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="I24" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="J24" s="33"/>
-    </row>
-    <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="40" t="n">
-        <f aca="false">SUM(F11:F24)</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="41"/>
-      <c r="J25" s="41"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -1994,7 +2175,7 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:E26"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2015,180 +2196,180 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
+      <c r="A1" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
+      <c r="A2" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="44" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" s="44" t="s">
+      <c r="B4" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="44" t="s">
+      <c r="E4" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="44" t="s">
-        <v>94</v>
+      <c r="F4" s="48" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="B5" s="46" t="s">
-        <v>96</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="E5" s="22" t="s">
+      <c r="A5" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="B5" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="26" t="s">
-        <v>99</v>
+      <c r="F5" s="38" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="47" t="s">
-        <v>100</v>
-      </c>
-      <c r="B6" s="48" t="s">
+      <c r="A6" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="49" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="50" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="38" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="52" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="49" t="s">
+        <v>136</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="51" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="52" t="s">
+        <v>141</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="E10" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="C6" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="45" t="s">
-        <v>105</v>
-      </c>
-      <c r="B7" s="46" t="s">
-        <v>106</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="B8" s="48" t="s">
-        <v>111</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="B9" s="46" t="s">
-        <v>116</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="B10" s="48" t="s">
-        <v>121</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="F10" s="26" t="s">
-        <v>124</v>
+      <c r="F10" s="38" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -2213,171 +2394,182 @@
     <tabColor rgb="FF2D6A4F"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="48"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="49" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
+      <c r="A1" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="C4" s="18" t="s">
+      <c r="B4" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="F4" s="18" t="s">
+      <c r="E4" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F4" s="19" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="46" t="s">
-        <v>129</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="D5" s="50" t="n">
+      <c r="B5" s="50" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" s="54" t="n">
         <v>19</v>
       </c>
-      <c r="E5" s="51" t="n">
+      <c r="E5" s="55" t="n">
         <f aca="false">D5/58</f>
         <v>0.327586206896552</v>
       </c>
-      <c r="F5" s="21" t="s">
-        <v>131</v>
+      <c r="F5" s="22" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="46" t="s">
-        <v>132</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="D6" s="50" t="n">
+      <c r="A6" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="54" t="n">
         <v>13</v>
       </c>
-      <c r="E6" s="51" t="n">
+      <c r="E6" s="55" t="n">
         <f aca="false">D6/58</f>
         <v>0.224137931034483</v>
       </c>
-      <c r="F6" s="21" t="s">
-        <v>134</v>
+      <c r="F6" s="22" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="46" t="s">
-        <v>135</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="D7" s="50" t="n">
+      <c r="A7" s="39" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="D7" s="54" t="n">
         <v>16</v>
       </c>
-      <c r="E7" s="51" t="n">
+      <c r="E7" s="55" t="n">
         <f aca="false">D7/58</f>
         <v>0.275862068965517</v>
       </c>
-      <c r="F7" s="21" t="s">
-        <v>137</v>
+      <c r="F7" s="22" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="B8" s="46" t="s">
-        <v>138</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="D8" s="50" t="n">
+      <c r="A8" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>158</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="D8" s="54" t="n">
         <v>16</v>
       </c>
-      <c r="E8" s="51" t="n">
+      <c r="E8" s="55" t="n">
         <f aca="false">D8/58</f>
         <v>0.275862068965517</v>
       </c>
-      <c r="F8" s="21" t="s">
-        <v>140</v>
+      <c r="F8" s="22" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="39" t="s">
-        <v>141</v>
-      </c>
-      <c r="B9" s="39"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="40" t="n">
+      <c r="A9" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="44" t="n">
         <f aca="false">SUM(D5:D8)</f>
         <v>64</v>
       </c>
-      <c r="E9" s="52" t="n">
+      <c r="E9" s="56" t="n">
         <f aca="false">D9/58</f>
         <v>1.10344827586207</v>
       </c>
-      <c r="F9" s="41"/>
+      <c r="F9" s="45"/>
+    </row>
+    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="57" t="s">
+        <v>162</v>
+      </c>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A11:F11"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/docs/ReFood_ProductBacklog.xlsx
+++ b/docs/ReFood_ProductBacklog.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="164">
   <si>
     <t xml:space="preserve">🌿  ReFood  —  Product Backlog</t>
   </si>
@@ -342,7 +342,7 @@
     <t xml:space="preserve">Como equipe, queremos testes automatizados no backend para garantir que mudanças futuras não quebrem funcionalidades existentes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Suíte Jest + Supertest cobrindo os endpoints de alimentos e categorias; script npm test funcional; roda contra uma branch de banco isolada no Neon</t>
+    <t xml:space="preserve">Suíte Jest + Supertest cobrindo os endpoints de alimentos, categorias e relatórios (30 testes, 3 suítes); script npm test funcional; roda com o pool do pg mockado, sem depender de conexão real com o banco.</t>
   </si>
   <si>
     <t xml:space="preserve">RNF-06</t>
@@ -351,7 +351,10 @@
     <t xml:space="preserve">Equipe</t>
   </si>
   <si>
-    <t xml:space="preserve">Nova story — não existia no backlog original (equipe de 4 pessoas não tinha essa frente listada).</t>
+    <t xml:space="preserve">Concluído (backend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entregue: backend/tests/ (helpers/mockPool.js + alimentos/categorias/relatorios.test.js). server.js ajustado pra exportar o app sem subir servidor durante os testes.</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL DE STORY POINTS</t>
@@ -2136,16 +2139,16 @@
       <c r="H25" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="I25" s="27" t="s">
-        <v>76</v>
+      <c r="I25" s="36" t="s">
+        <v>109</v>
       </c>
       <c r="J25" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="43" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B26" s="43"/>
       <c r="C26" s="43"/>
@@ -2206,7 +2209,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="46" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B1" s="46"/>
       <c r="C1" s="46"/>
@@ -2216,7 +2219,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="47" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B2" s="47"/>
       <c r="C2" s="47"/>
@@ -2237,10 +2240,10 @@
         <v>15</v>
       </c>
       <c r="B4" s="48" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C4" s="48" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D4" s="48" t="s">
         <v>17</v>
@@ -2249,107 +2252,107 @@
         <v>19</v>
       </c>
       <c r="F4" s="48" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="49" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E5" s="23" t="s">
         <v>29</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="51" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E6" s="23" t="s">
         <v>29</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="49" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E7" s="23" t="s">
         <v>29</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="51" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E8" s="23" t="s">
         <v>29</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="49" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B9" s="50" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E9" s="35" t="s">
         <v>42</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2357,19 +2360,19 @@
         <v>107</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E10" s="41" t="s">
         <v>101</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2407,7 +2410,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="53" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B1" s="53"/>
       <c r="C1" s="53"/>
@@ -2417,7 +2420,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2438,7 +2441,7 @@
         <v>21</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>8</v>
@@ -2447,7 +2450,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F4" s="19" t="s">
         <v>24</v>
@@ -2458,10 +2461,10 @@
         <v>30</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D5" s="54" t="n">
         <v>19</v>
@@ -2471,7 +2474,7 @@
         <v>0.327586206896552</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2479,10 +2482,10 @@
         <v>75</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D6" s="54" t="n">
         <v>13</v>
@@ -2492,7 +2495,7 @@
         <v>0.224137931034483</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2500,10 +2503,10 @@
         <v>81</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D7" s="54" t="n">
         <v>16</v>
@@ -2513,7 +2516,7 @@
         <v>0.275862068965517</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2521,10 +2524,10 @@
         <v>102</v>
       </c>
       <c r="B8" s="50" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D8" s="54" t="n">
         <v>16</v>
@@ -2534,12 +2537,12 @@
         <v>0.275862068965517</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="43" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B9" s="43"/>
       <c r="C9" s="43"/>
@@ -2555,7 +2558,7 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="57" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B11" s="57"/>
       <c r="C11" s="57"/>
